--- a/slots/resources/sample/BaseLineFree.xlsx
+++ b/slots/resources/sample/BaseLineFree.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28925"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspace\gameserver\slots\resources\sample\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD2BF15F-86F0-4381-B30C-DB19E9ABB79E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDFCAB7C-443B-4FAC-9372-13B675587132}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="35295" yWindow="1350" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="30450" yWindow="915" windowWidth="21600" windowHeight="13410" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BaseLineFree" sheetId="1" r:id="rId1"/>
@@ -244,7 +244,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="41">
   <si>
     <t>id</t>
   </si>
@@ -327,9 +327,6 @@
     <t>gamePlayCalc</t>
   </si>
   <si>
-    <t>2,1;2,2;2,3;2,4</t>
-  </si>
-  <si>
     <t>0,false</t>
   </si>
   <si>
@@ -337,9 +334,6 @@
   </si>
   <si>
     <t>4个拉火车</t>
-  </si>
-  <si>
-    <t>2,1</t>
   </si>
   <si>
     <t>1:18,15</t>
@@ -367,6 +361,18 @@
   </si>
   <si>
     <t>appointElementList</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,2</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,2;2,2;3,2;4,2</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>map&lt;int{,}int&gt;{;}</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
 </sst>
@@ -536,7 +542,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>789464</xdr:colOff>
+      <xdr:colOff>1075214</xdr:colOff>
       <xdr:row>45</xdr:row>
       <xdr:rowOff>176530</xdr:rowOff>
     </xdr:to>
@@ -623,7 +629,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>789464</xdr:colOff>
+      <xdr:colOff>1075214</xdr:colOff>
       <xdr:row>51</xdr:row>
       <xdr:rowOff>176530</xdr:rowOff>
     </xdr:to>
@@ -710,7 +716,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>789464</xdr:colOff>
+      <xdr:colOff>1075214</xdr:colOff>
       <xdr:row>51</xdr:row>
       <xdr:rowOff>176530</xdr:rowOff>
     </xdr:to>
@@ -797,7 +803,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>789464</xdr:colOff>
+      <xdr:colOff>1075214</xdr:colOff>
       <xdr:row>51</xdr:row>
       <xdr:rowOff>176530</xdr:rowOff>
     </xdr:to>
@@ -1134,7 +1140,7 @@
     <col min="2" max="2" width="11.375" style="4" customWidth="1"/>
     <col min="3" max="3" width="8.125" style="5" customWidth="1"/>
     <col min="4" max="4" width="10.625" style="5" customWidth="1"/>
-    <col min="5" max="5" width="17.625" style="5" customWidth="1"/>
+    <col min="5" max="5" width="13.875" style="5" customWidth="1"/>
     <col min="6" max="6" width="14.75" style="5" customWidth="1"/>
     <col min="7" max="7" width="30.125" style="5" customWidth="1"/>
     <col min="8" max="9" width="21.5" style="5" customWidth="1"/>
@@ -1200,7 +1206,7 @@
         <v>13</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="F2" s="5" t="s">
         <v>15</v>
@@ -1230,7 +1236,7 @@
         <v>0</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C3" s="5" t="s">
         <v>19</v>
@@ -1245,7 +1251,7 @@
         <v>22</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="H3" s="5" t="s">
         <v>23</v>
@@ -1290,27 +1296,27 @@
         <v>51</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="F5" s="5"/>
       <c r="G5" s="5" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="I5" s="5"/>
       <c r="J5" s="5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="K5" s="5">
         <v>5</v>
       </c>
       <c r="L5" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="M5" s="5" t="s">
         <v>29</v>
-      </c>
-      <c r="M5" s="5" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.15">
@@ -1327,25 +1333,25 @@
         <v>52</v>
       </c>
       <c r="E6" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="G6" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="H6" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="G6" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="H6" s="5" t="s">
-        <v>33</v>
-      </c>
       <c r="J6" s="5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="K6" s="5">
         <v>5</v>
       </c>
       <c r="L6" s="5" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="M6" s="5" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>

--- a/slots/resources/sample/BaseLineFree.xlsx
+++ b/slots/resources/sample/BaseLineFree.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspace\gameserver\slots\resources\sample\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDFCAB7C-443B-4FAC-9372-13B675587132}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B77F51C4-F4D3-4DBA-93B1-06FD9FD54892}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30450" yWindow="915" windowWidth="21600" windowHeight="13410" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BaseLineFree" sheetId="1" r:id="rId1"/>
@@ -336,12 +336,6 @@
     <t>4个拉火车</t>
   </si>
   <si>
-    <t>1:18,15</t>
-  </si>
-  <si>
-    <t>1,2</t>
-  </si>
-  <si>
     <t>1,5</t>
   </si>
   <si>
@@ -373,6 +367,14 @@
   </si>
   <si>
     <t>map&lt;int{,}int&gt;{;}</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,1</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>1:18,15</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
 </sst>
@@ -1206,7 +1208,7 @@
         <v>13</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F2" s="5" t="s">
         <v>15</v>
@@ -1236,7 +1238,7 @@
         <v>0</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C3" s="5" t="s">
         <v>19</v>
@@ -1251,7 +1253,7 @@
         <v>22</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="H3" s="5" t="s">
         <v>23</v>
@@ -1296,14 +1298,14 @@
         <v>51</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F5" s="5"/>
       <c r="G5" s="5" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="I5" s="5"/>
       <c r="J5" s="5" t="s">
@@ -1333,13 +1335,13 @@
         <v>52</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="J6" s="5" t="s">
         <v>27</v>
@@ -1348,10 +1350,10 @@
         <v>5</v>
       </c>
       <c r="L6" s="5" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="M6" s="5" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
   </sheetData>

--- a/slots/resources/sample/BaseLineFree.xlsx
+++ b/slots/resources/sample/BaseLineFree.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29029"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspace\gameserver\slots\resources\sample\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B77F51C4-F4D3-4DBA-93B1-06FD9FD54892}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1455AD42-A427-4C7C-81DE-EE49522A365D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="31425" yWindow="2715" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BaseLineFree" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,6 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>普通: 1
@@ -47,7 +46,6 @@
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">Mr.M:
@@ -57,7 +55,6 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>线路玩法，
@@ -92,7 +89,6 @@
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">Mr.M:
@@ -102,7 +98,6 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">路线从1-5的坐标
@@ -118,7 +113,6 @@
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">Mr.M:
@@ -128,7 +122,6 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>中奖结果由指定的元素组成，格式为[元素1ID,元素2ID……]
@@ -144,7 +137,6 @@
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">Mr.M:
@@ -154,7 +146,6 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>该中奖线的元素至少有多少个元素组成</t>
@@ -168,7 +159,6 @@
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">Mr.M:
@@ -178,7 +168,6 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>中奖算法否为双向均可中奖，格式：是或否，或无，无代表非连线玩法</t>
@@ -191,7 +180,6 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>加:1
@@ -212,7 +200,6 @@
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">Mr.M:
@@ -222,7 +209,6 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>方向算法有加或最大
@@ -244,7 +230,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="39">
   <si>
     <t>id</t>
   </si>
@@ -288,19 +274,22 @@
     <t>int</t>
   </si>
   <si>
+    <t>map&lt;int{,}int&gt;{;}</t>
+  </si>
+  <si>
+    <t>list&lt;map&lt;int{-}int&gt;{,}&gt;{;}</t>
+  </si>
+  <si>
+    <t>map&lt;int{:}List&lt;int&gt;{,}&gt;{;}</t>
+  </si>
+  <si>
     <t>List&lt;List&lt;int&gt;{,}&gt;{;}</t>
   </si>
   <si>
-    <t>list&lt;map&lt;int{-}int&gt;{,}&gt;{;}</t>
-  </si>
-  <si>
-    <t>map&lt;int{:}List&lt;int&gt;{,}&gt;{;}</t>
-  </si>
-  <si>
     <t>map&lt;int{,}bool&gt;{;}</t>
   </si>
   <si>
-    <t>map&lt;int{,}int&gt;{;}</t>
+    <t>gameType</t>
   </si>
   <si>
     <t>lineType</t>
@@ -327,6 +316,12 @@
     <t>gamePlayCalc</t>
   </si>
   <si>
+    <t>1,2;2,2;3,2;4,2</t>
+  </si>
+  <si>
+    <t>1:19,16;2:20,16;3:21,16;4:22,16</t>
+  </si>
+  <si>
     <t>0,false</t>
   </si>
   <si>
@@ -336,45 +331,23 @@
     <t>4个拉火车</t>
   </si>
   <si>
+    <t>1,2</t>
+  </si>
+  <si>
+    <t>1,1</t>
+  </si>
+  <si>
     <t>1,5</t>
   </si>
   <si>
     <t>黄金列车</t>
-  </si>
-  <si>
-    <t>1,2;2,2;3,2;4,2</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>gameType</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>1:19,16;2:20,16;3:21,16;4:22,16</t>
-    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>appointElementList</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
-    <t>1,2</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>1,2;2,2;3,2;4,2</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>map&lt;int{,}int&gt;{;}</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>1,1</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>1:18,15</t>
+    <t>1:15</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
 </sst>
@@ -382,7 +355,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -394,15 +367,41 @@
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="微软雅黑"/>
-      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
-      <family val="3"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
@@ -410,32 +409,6 @@
       <name val="微软雅黑"/>
       <family val="2"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="微软雅黑"/>
-      <family val="2"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -481,7 +454,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -491,13 +464,13 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -508,6 +481,12 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -526,13 +505,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/customStorage/customStorage.xml><?xml version="1.0" encoding="utf-8"?>
-<customStorage xmlns="https://web.wps.cn/et/2018/main">
-  <book/>
-  <sheets/>
-</customStorage>
-</file>
-
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
@@ -545,8 +517,8 @@
     <xdr:to>
       <xdr:col>8</xdr:col>
       <xdr:colOff>1075214</xdr:colOff>
-      <xdr:row>45</xdr:row>
-      <xdr:rowOff>176530</xdr:rowOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>28364</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -562,7 +534,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="685800" y="0"/>
-          <a:ext cx="9505315" cy="9815830"/>
+          <a:ext cx="9485630" cy="9815830"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -602,7 +574,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="685800" y="1257300"/>
+          <a:off x="685800" y="838200"/>
           <a:ext cx="9505315" cy="9815830"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -633,7 +605,7 @@
       <xdr:col>8</xdr:col>
       <xdr:colOff>1075214</xdr:colOff>
       <xdr:row>51</xdr:row>
-      <xdr:rowOff>176530</xdr:rowOff>
+      <xdr:rowOff>176529</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -648,8 +620,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="685800" y="1257300"/>
-          <a:ext cx="9505315" cy="9815830"/>
+          <a:off x="685800" y="838200"/>
+          <a:ext cx="9485630" cy="9815830"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -689,7 +661,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="685800" y="1257300"/>
+          <a:off x="685800" y="838200"/>
           <a:ext cx="9505315" cy="9815830"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -720,7 +692,7 @@
       <xdr:col>8</xdr:col>
       <xdr:colOff>1075214</xdr:colOff>
       <xdr:row>51</xdr:row>
-      <xdr:rowOff>176530</xdr:rowOff>
+      <xdr:rowOff>176529</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -735,8 +707,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="685800" y="1257300"/>
-          <a:ext cx="9505315" cy="9815830"/>
+          <a:off x="685800" y="838200"/>
+          <a:ext cx="9485630" cy="9815830"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -776,7 +748,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="685800" y="1257300"/>
+          <a:off x="685800" y="838200"/>
           <a:ext cx="9505315" cy="9815830"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -807,7 +779,7 @@
       <xdr:col>8</xdr:col>
       <xdr:colOff>1075214</xdr:colOff>
       <xdr:row>51</xdr:row>
-      <xdr:rowOff>176530</xdr:rowOff>
+      <xdr:rowOff>176529</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -822,8 +794,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="685800" y="1257300"/>
-          <a:ext cx="9505315" cy="9815830"/>
+          <a:off x="685800" y="838200"/>
+          <a:ext cx="9485630" cy="9815830"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -863,7 +835,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="685800" y="1257300"/>
+          <a:off x="685800" y="838200"/>
           <a:ext cx="9505315" cy="9815830"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1139,18 +1111,18 @@
   <dimension ref="A1:M6"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="2" max="2" width="11.375" style="4" customWidth="1"/>
-    <col min="3" max="3" width="8.125" style="5" customWidth="1"/>
-    <col min="4" max="4" width="10.625" style="5" customWidth="1"/>
-    <col min="5" max="5" width="13.875" style="5" customWidth="1"/>
-    <col min="6" max="6" width="14.75" style="5" customWidth="1"/>
-    <col min="7" max="7" width="30.125" style="5" customWidth="1"/>
-    <col min="8" max="9" width="21.5" style="5" customWidth="1"/>
-    <col min="10" max="10" width="16" style="5" customWidth="1"/>
-    <col min="11" max="11" width="12.25" style="5" customWidth="1"/>
-    <col min="12" max="12" width="16" style="5" customWidth="1"/>
-    <col min="13" max="13" width="9" style="5"/>
-    <col min="14" max="16384" width="9" style="3"/>
+    <col min="2" max="2" width="11.375" style="3" customWidth="1"/>
+    <col min="3" max="3" width="8.125" style="4" customWidth="1"/>
+    <col min="4" max="4" width="10.625" style="4" customWidth="1"/>
+    <col min="5" max="5" width="13.875" style="4" customWidth="1"/>
+    <col min="6" max="6" width="14.75" style="4" customWidth="1"/>
+    <col min="7" max="7" width="30.125" style="4" customWidth="1"/>
+    <col min="8" max="9" width="21.5" style="4" customWidth="1"/>
+    <col min="10" max="10" width="16" style="4" customWidth="1"/>
+    <col min="11" max="11" width="12.25" style="4" customWidth="1"/>
+    <col min="12" max="12" width="16" style="4" customWidth="1"/>
+    <col min="13" max="13" width="9" style="4"/>
+    <col min="14" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" s="1" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.15">
@@ -1198,162 +1170,162 @@
       <c r="A2" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D2" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="E2" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="F2" s="5" t="s">
+      <c r="E2" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="G2" s="5" t="s">
+      <c r="G2" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="H2" s="5" t="s">
+      <c r="H2" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="J2" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="K2" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="L2" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="I2" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="J2" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="K2" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="L2" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="M2" s="5"/>
+      <c r="M2" s="4"/>
     </row>
-    <row r="3" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:13" s="2" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="C3" s="5" t="s">
+      <c r="B3" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="C3" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="D3" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="F3" s="5" t="s">
+      <c r="E3" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="G3" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="H3" s="5" t="s">
+      <c r="F3" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="I3" s="5" t="s">
+      <c r="G3" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="H3" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="J3" s="5" t="s">
+      <c r="I3" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="K3" s="5" t="s">
+      <c r="J3" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="L3" s="5"/>
-      <c r="M3" s="5"/>
+      <c r="K3" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="L3" s="4"/>
+      <c r="M3" s="4"/>
     </row>
-    <row r="4" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="B4" s="4"/>
-      <c r="C4" s="5"/>
-      <c r="D4" s="5"/>
-      <c r="E4" s="5"/>
-      <c r="F4" s="5"/>
-      <c r="G4" s="5"/>
-      <c r="H4" s="5"/>
-      <c r="I4" s="5"/>
-      <c r="J4" s="5"/>
-      <c r="K4" s="5"/>
-      <c r="L4" s="5"/>
-      <c r="M4" s="5"/>
+    <row r="4" spans="1:13" s="2" customFormat="1" ht="38.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B4" s="3"/>
+      <c r="C4" s="4"/>
+      <c r="D4" s="4"/>
+      <c r="E4" s="4"/>
+      <c r="F4" s="4"/>
+      <c r="G4" s="4"/>
+      <c r="H4" s="4"/>
+      <c r="I4" s="4"/>
+      <c r="J4" s="4"/>
+      <c r="K4" s="4"/>
+      <c r="L4" s="4"/>
+      <c r="M4" s="4"/>
     </row>
     <row r="5" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A5" s="2">
         <v>1</v>
       </c>
-      <c r="B5" s="4">
+      <c r="B5" s="3">
         <v>100100</v>
       </c>
-      <c r="C5" s="5">
+      <c r="C5" s="4">
         <v>2</v>
       </c>
-      <c r="D5" s="5">
+      <c r="D5" s="4">
         <v>51</v>
       </c>
-      <c r="E5" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="F5" s="5"/>
-      <c r="G5" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="H5" s="5" t="s">
+      <c r="E5" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="F5" s="4"/>
+      <c r="G5" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="I5" s="4"/>
+      <c r="J5" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="K5" s="4">
+        <v>5</v>
+      </c>
+      <c r="L5" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="M5" s="4" t="s">
         <v>32</v>
-      </c>
-      <c r="I5" s="5"/>
-      <c r="J5" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="K5" s="5">
-        <v>5</v>
-      </c>
-      <c r="L5" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="M5" s="5" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A6" s="2">
         <v>2</v>
       </c>
-      <c r="B6" s="4">
+      <c r="B6" s="3">
         <v>100100</v>
       </c>
-      <c r="C6" s="5">
+      <c r="C6" s="4">
         <v>2</v>
       </c>
-      <c r="D6" s="5">
+      <c r="D6" s="4">
         <v>52</v>
       </c>
-      <c r="E6" s="5" t="s">
+      <c r="E6" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="G6" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="H6" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="J6" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="K6" s="4">
+        <v>5</v>
+      </c>
+      <c r="L6" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="M6" s="4" t="s">
         <v>36</v>
-      </c>
-      <c r="G6" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="H6" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="J6" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="K6" s="5">
-        <v>5</v>
-      </c>
-      <c r="L6" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="M6" s="5" t="s">
-        <v>31</v>
       </c>
     </row>
   </sheetData>
